--- a/examples/catl-2025/deliverables/workbook.xlsx
+++ b/examples/catl-2025/deliverables/workbook.xlsx
@@ -24,16 +24,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Findings!$A$1:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Procedures!$A$1:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Readme!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reconciliations!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reconciliations!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Requests!$A$1:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sources!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sources!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="514">
   <si>
     <t>字段 / field</t>
   </si>
@@ -1094,13 +1094,16 @@
     <t>容差依据</t>
   </si>
   <si>
+    <t>未测试原因</t>
+  </si>
+  <si>
     <t>R_BS</t>
   </si>
   <si>
     <t>资产负债关系</t>
   </si>
   <si>
-    <t>within_precision</t>
+    <t>within_input_tolerance</t>
   </si>
   <si>
     <t>基础单位人民币；原表以千元披露。按参加计算项目的独立舍入上界保留残差，不将容差内残差强制归零。</t>
@@ -1170,6 +1173,9 @@
   </si>
   <si>
     <t>SHA256</t>
+  </si>
+  <si>
+    <t>时间证据与限制</t>
   </si>
   <si>
     <t>AR</t>
@@ -2127,7 +2133,7 @@
         <v>1000</v>
       </c>
       <c r="F2" s="3">
-        <f>D2*E2</f>
+        <f>IF(COUNT(D2,E2)=2,D2*E2,NA())</f>
         <v>423701834000.0</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -2180,7 +2186,7 @@
         <v>1000</v>
       </c>
       <c r="F3" s="3">
-        <f>D3*E3</f>
+        <f>IF(COUNT(D3,E3)=2,D3*E3,NA())</f>
         <v>362012554000.0</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -2233,7 +2239,7 @@
         <v>1000</v>
       </c>
       <c r="F4" s="3">
-        <f>D4*E4</f>
+        <f>IF(COUNT(D4,E4)=2,D4*E4,NA())</f>
         <v>312383297000.0</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -2286,7 +2292,7 @@
         <v>1000</v>
       </c>
       <c r="F5" s="3">
-        <f>D5*E5</f>
+        <f>IF(COUNT(D5,E5)=2,D5*E5,NA())</f>
         <v>273518959000.0</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -2339,7 +2345,7 @@
         <v>1000</v>
       </c>
       <c r="F6" s="3">
-        <f>D6*E6</f>
+        <f>IF(COUNT(D6,E6)=2,D6*E6,NA())</f>
         <v>76786309000.0</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -2392,7 +2398,7 @@
         <v>1000</v>
       </c>
       <c r="F7" s="3">
-        <f>D7*E7</f>
+        <f>IF(COUNT(D7,E7)=2,D7*E7,NA())</f>
         <v>54006794000.0</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -2445,7 +2451,7 @@
         <v>1000</v>
       </c>
       <c r="F8" s="3">
-        <f>D8*E8</f>
+        <f>IF(COUNT(D8,E8)=2,D8*E8,NA())</f>
         <v>133219982000.0</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -2498,7 +2504,7 @@
         <v>1000</v>
       </c>
       <c r="F9" s="3">
-        <f>D9*E9</f>
+        <f>IF(COUNT(D9,E9)=2,D9*E9,NA())</f>
         <v>96990345000.0</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -2551,7 +2557,7 @@
         <v>1000</v>
       </c>
       <c r="F10" s="3">
-        <f>D10*E10</f>
+        <f>IF(COUNT(D10,E10)=2,D10*E10,NA())</f>
         <v>299929741000.0</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -2602,7 +2608,7 @@
         <v>1000</v>
       </c>
       <c r="F11" s="3">
-        <f>D11*E11</f>
+        <f>IF(COUNT(D11,E11)=2,D11*E11,NA())</f>
         <v>270159734000.0</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -2653,7 +2659,7 @@
         <v>1000</v>
       </c>
       <c r="F12" s="3">
-        <f>D12*E12</f>
+        <f>IF(COUNT(D12,E12)=2,D12*E12,NA())</f>
         <v>974827544000.0</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -2704,7 +2710,7 @@
         <v>1000</v>
       </c>
       <c r="F13" s="3">
-        <f>D13*E13</f>
+        <f>IF(COUNT(D13,E13)=2,D13*E13,NA())</f>
         <v>786658123000.0</v>
       </c>
       <c r="G13" s="2" t="s">
@@ -2755,7 +2761,7 @@
         <v>1000</v>
       </c>
       <c r="F14" s="3">
-        <f>D14*E14</f>
+        <f>IF(COUNT(D14,E14)=2,D14*E14,NA())</f>
         <v>371026324000.0</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -2806,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="F15" s="3">
-        <f>D15*E15</f>
+        <f>IF(COUNT(D15,E15)=2,D15*E15,NA())</f>
         <v>273456174000.0</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -2857,7 +2863,7 @@
         <v>1000</v>
       </c>
       <c r="F16" s="3">
-        <f>D16*E16</f>
+        <f>IF(COUNT(D16,E16)=2,D16*E16,NA())</f>
         <v>337107747000.0</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -2908,7 +2914,7 @@
         <v>1000</v>
       </c>
       <c r="F17" s="3">
-        <f>D17*E17</f>
+        <f>IF(COUNT(D17,E17)=2,D17*E17,NA())</f>
         <v>246930033000.0</v>
       </c>
       <c r="G17" s="2" t="s">
@@ -2959,7 +2965,7 @@
         <v>1000</v>
       </c>
       <c r="F18" s="3">
-        <f>D18*E18</f>
+        <f>IF(COUNT(D18,E18)=2,D18*E18,NA())</f>
         <v>94526239000.0</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -3010,7 +3016,7 @@
         <v>1000</v>
       </c>
       <c r="F19" s="3">
-        <f>D19*E19</f>
+        <f>IF(COUNT(D19,E19)=2,D19*E19,NA())</f>
         <v>59835533000.0</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -3061,7 +3067,7 @@
         <v>1000</v>
       </c>
       <c r="F20" s="3">
-        <f>D20*E20</f>
+        <f>IF(COUNT(D20,E20)=2,D20*E20,NA())</f>
         <v>76403264000.0</v>
       </c>
       <c r="G20" s="2" t="s">
@@ -3112,7 +3118,7 @@
         <v>1000</v>
       </c>
       <c r="F21" s="3">
-        <f>D21*E21</f>
+        <f>IF(COUNT(D21,E21)=2,D21*E21,NA())</f>
         <v>64135510000.0</v>
       </c>
       <c r="G21" s="2" t="s">
@@ -3163,7 +3169,7 @@
         <v>1000</v>
       </c>
       <c r="F22" s="3">
-        <f>D22*E22</f>
+        <f>IF(COUNT(D22,E22)=2,D22*E22,NA())</f>
         <v>160328962000.0</v>
       </c>
       <c r="G22" s="2" t="s">
@@ -3214,7 +3220,7 @@
         <v>1000</v>
       </c>
       <c r="F23" s="3">
-        <f>D23*E23</f>
+        <f>IF(COUNT(D23,E23)=2,D23*E23,NA())</f>
         <v>130977408000.0</v>
       </c>
       <c r="G23" s="2" t="s">
@@ -3265,7 +3271,7 @@
         <v>1000</v>
       </c>
       <c r="F24" s="3">
-        <f>D24*E24</f>
+        <f>IF(COUNT(D24,E24)=2,D24*E24,NA())</f>
         <v>49233377000.0</v>
       </c>
       <c r="G24" s="2" t="s">
@@ -3316,7 +3322,7 @@
         <v>1000</v>
       </c>
       <c r="F25" s="3">
-        <f>D25*E25</f>
+        <f>IF(COUNT(D25,E25)=2,D25*E25,NA())</f>
         <v>27834446000.0</v>
       </c>
       <c r="G25" s="2" t="s">
@@ -3367,7 +3373,7 @@
         <v>1000</v>
       </c>
       <c r="F26" s="3">
-        <f>D26*E26</f>
+        <f>IF(COUNT(D26,E26)=2,D26*E26,NA())</f>
         <v>37222781000.0</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -3418,7 +3424,7 @@
         <v>1000</v>
       </c>
       <c r="F27" s="3">
-        <f>D27*E27</f>
+        <f>IF(COUNT(D27,E27)=2,D27*E27,NA())</f>
         <v>44362409000.0</v>
       </c>
       <c r="G27" s="2" t="s">
@@ -3469,7 +3475,7 @@
         <v>1000</v>
       </c>
       <c r="F28" s="3">
-        <f>D28*E28</f>
+        <f>IF(COUNT(D28,E28)=2,D28*E28,NA())</f>
         <v>51233080000.0</v>
       </c>
       <c r="G28" s="2" t="s">
@@ -3520,7 +3526,7 @@
         <v>1000</v>
       </c>
       <c r="F29" s="3">
-        <f>D29*E29</f>
+        <f>IF(COUNT(D29,E29)=2,D29*E29,NA())</f>
         <v>39070181000.0</v>
       </c>
       <c r="G29" s="2" t="s">
@@ -3571,7 +3577,7 @@
         <v>1000</v>
       </c>
       <c r="F30" s="3">
-        <f>D30*E30</f>
+        <f>IF(COUNT(D30,E30)=2,D30*E30,NA())</f>
         <v>119601197000.0</v>
       </c>
       <c r="G30" s="2" t="s">
@@ -3622,7 +3628,7 @@
         <v>1000</v>
       </c>
       <c r="F31" s="3">
-        <f>D31*E31</f>
+        <f>IF(COUNT(D31,E31)=2,D31*E31,NA())</f>
         <v>136346553000.0</v>
       </c>
       <c r="G31" s="2" t="s">
@@ -3673,7 +3679,7 @@
         <v>1000</v>
       </c>
       <c r="F32" s="3">
-        <f>D32*E32</f>
+        <f>IF(COUNT(D32,E32)=2,D32*E32,NA())</f>
         <v>316506369000.0</v>
       </c>
       <c r="G32" s="2" t="s">
@@ -3726,7 +3732,7 @@
         <v>1000</v>
       </c>
       <c r="F33" s="3">
-        <f>D33*E33</f>
+        <f>IF(COUNT(D33,E33)=2,D33*E33,NA())</f>
         <v>253041337000.0</v>
       </c>
       <c r="G33" s="2" t="s">
@@ -3779,7 +3785,7 @@
         <v>1000</v>
       </c>
       <c r="F34" s="3">
-        <f>D34*E34</f>
+        <f>IF(COUNT(D34,E34)=2,D34*E34,NA())</f>
         <v>62439820000.0</v>
       </c>
       <c r="G34" s="2" t="s">
@@ -3832,7 +3838,7 @@
         <v>1000</v>
       </c>
       <c r="F35" s="3">
-        <f>D35*E35</f>
+        <f>IF(COUNT(D35,E35)=2,D35*E35,NA())</f>
         <v>57290460000.0</v>
       </c>
       <c r="G35" s="2" t="s">
@@ -3885,7 +3891,7 @@
         <v>1000</v>
       </c>
       <c r="F36" s="3">
-        <f>D36*E36</f>
+        <f>IF(COUNT(D36,E36)=2,D36*E36,NA())</f>
         <v>21860936000.0</v>
       </c>
       <c r="G36" s="2" t="s">
@@ -3938,7 +3944,7 @@
         <v>1000</v>
       </c>
       <c r="F37" s="3">
-        <f>D37*E37</f>
+        <f>IF(COUNT(D37,E37)=2,D37*E37,NA())</f>
         <v>28699935000.0</v>
       </c>
       <c r="G37" s="2" t="s">
@@ -3991,7 +3997,7 @@
         <v>1000</v>
       </c>
       <c r="F38" s="3">
-        <f>D38*E38</f>
+        <f>IF(COUNT(D38,E38)=2,D38*E38,NA())</f>
         <v>72201282000.0</v>
       </c>
       <c r="G38" s="2" t="s">
@@ -4044,7 +4050,7 @@
         <v>1000</v>
       </c>
       <c r="F39" s="3">
-        <f>D39*E39</f>
+        <f>IF(COUNT(D39,E39)=2,D39*E39,NA())</f>
         <v>4585027000.0</v>
       </c>
       <c r="G39" s="2" t="s">
@@ -4097,7 +4103,7 @@
         <v>1000</v>
       </c>
       <c r="F40" s="3">
-        <f>D40*E40</f>
+        <f>IF(COUNT(D40,E40)=2,D40*E40,NA())</f>
         <v>-94475790000.0</v>
       </c>
       <c r="G40" s="2" t="s">
@@ -4150,7 +4156,7 @@
         <v>1000</v>
       </c>
       <c r="F41" s="3">
-        <f>D41*E41</f>
+        <f>IF(COUNT(D41,E41)=2,D41*E41,NA())</f>
         <v>-6309543000.0</v>
       </c>
       <c r="G41" s="2" t="s">
@@ -4203,7 +4209,7 @@
         <v>1000</v>
       </c>
       <c r="F42" s="3">
-        <f>D42*E42</f>
+        <f>IF(COUNT(D42,E42)=2,D42*E42,NA())</f>
         <v>-2664640000.0</v>
       </c>
       <c r="G42" s="2" t="s">
@@ -4256,7 +4262,7 @@
         <v>1000</v>
       </c>
       <c r="F43" s="3">
-        <f>D43*E43</f>
+        <f>IF(COUNT(D43,E43)=2,D43*E43,NA())</f>
         <v>29770008000.0</v>
       </c>
       <c r="G43" s="2" t="s">
@@ -4309,7 +4315,7 @@
         <v>1000</v>
       </c>
       <c r="F44" s="3">
-        <f>D44*E44</f>
+        <f>IF(COUNT(D44,E44)=2,D44*E44,NA())</f>
         <v>42344558000.0</v>
       </c>
       <c r="G44" s="2" t="s">
@@ -4362,7 +4368,7 @@
         <v>1000</v>
       </c>
       <c r="F45" s="3">
-        <f>D45*E45</f>
+        <f>IF(COUNT(D45,E45)=2,D45*E45,NA())</f>
         <v>84006523000.0</v>
       </c>
       <c r="G45" s="2" t="s">
@@ -4415,7 +4421,7 @@
         <v>1000</v>
       </c>
       <c r="F46" s="3">
-        <f>D46*E46</f>
+        <f>IF(COUNT(D46,E46)=2,D46*E46,NA())</f>
         <v>40416391000.0</v>
       </c>
       <c r="G46" s="2" t="s">
@@ -4468,7 +4474,7 @@
         <v>1000</v>
       </c>
       <c r="F47" s="3">
-        <f>D47*E47</f>
+        <f>IF(COUNT(D47,E47)=2,D47*E47,NA())</f>
         <v>-26842954000.0</v>
       </c>
       <c r="G47" s="2" t="s">
@@ -4521,7 +4527,7 @@
         <v>1000</v>
       </c>
       <c r="F48" s="3">
-        <f>D48*E48</f>
+        <f>IF(COUNT(D48,E48)=2,D48*E48,NA())</f>
         <v>-9811000.0</v>
       </c>
       <c r="G48" s="2" t="s">
@@ -4574,7 +4580,7 @@
         <v>1000</v>
       </c>
       <c r="F49" s="3">
-        <f>D49*E49</f>
+        <f>IF(COUNT(D49,E49)=2,D49*E49,NA())</f>
         <v>39790079000.0</v>
       </c>
       <c r="G49" s="2" t="s">
@@ -4627,7 +4633,7 @@
         <v>1000</v>
       </c>
       <c r="F50" s="3">
-        <f>D50*E50</f>
+        <f>IF(COUNT(D50,E50)=2,D50*E50,NA())</f>
         <v>-54608510000.0</v>
       </c>
       <c r="G50" s="2" t="s">
@@ -4680,7 +4686,7 @@
         <v>1000</v>
       </c>
       <c r="F51" s="3">
-        <f>D51*E51</f>
+        <f>IF(COUNT(D51,E51)=2,D51*E51,NA())</f>
         <v>-1926925000.0</v>
       </c>
       <c r="G51" s="2" t="s">
@@ -4733,7 +4739,7 @@
         <v>1000</v>
       </c>
       <c r="F52" s="3">
-        <f>D52*E52</f>
+        <f>IF(COUNT(D52,E52)=2,D52*E52,NA())</f>
         <v>2659992000.0</v>
       </c>
       <c r="G52" s="2" t="s">
@@ -4786,7 +4792,7 @@
         <v>1000</v>
       </c>
       <c r="F53" s="3">
-        <f>D53*E53</f>
+        <f>IF(COUNT(D53,E53)=2,D53*E53,NA())</f>
         <v>60616240000.0</v>
       </c>
       <c r="G53" s="2" t="s">
@@ -4839,7 +4845,7 @@
         <v>1000</v>
       </c>
       <c r="F54" s="3">
-        <f>D54*E54</f>
+        <f>IF(COUNT(D54,E54)=2,D54*E54,NA())</f>
         <v>603801220000.0</v>
       </c>
       <c r="G54" s="2" t="s">
@@ -4890,7 +4896,7 @@
         <v>1000</v>
       </c>
       <c r="F55" s="3">
-        <f>D55*E55</f>
+        <f>IF(COUNT(D55,E55)=2,D55*E55,NA())</f>
         <v>333512927000.0</v>
       </c>
       <c r="G55" s="2" t="s">
@@ -4941,7 +4947,7 @@
         <v>1000</v>
       </c>
       <c r="F56" s="3">
-        <f>D56*E56</f>
+        <f>IF(COUNT(D56,E56)=2,D56*E56,NA())</f>
         <v>33583185000.0</v>
       </c>
       <c r="G56" s="2" t="s">
@@ -4992,7 +4998,7 @@
         <v>1000</v>
       </c>
       <c r="F57" s="3">
-        <f>D57*E57</f>
+        <f>IF(COUNT(D57,E57)=2,D57*E57,NA())</f>
         <v>18428631000.0</v>
       </c>
       <c r="G57" s="2" t="s">
@@ -5043,7 +5049,7 @@
         <v>1000</v>
       </c>
       <c r="F58" s="3">
-        <f>D58*E58</f>
+        <f>IF(COUNT(D58,E58)=2,D58*E58,NA())</f>
         <v>461587000.0</v>
       </c>
       <c r="G58" s="2" t="s">
@@ -5094,7 +5100,7 @@
         <v>1000</v>
       </c>
       <c r="F59" s="3">
-        <f>D59*E59</f>
+        <f>IF(COUNT(D59,E59)=2,D59*E59,NA())</f>
         <v>14692968000.0</v>
       </c>
       <c r="G59" s="2" t="s">
@@ -5145,7 +5151,7 @@
         <v>1000</v>
       </c>
       <c r="F60" s="3">
-        <f>D60*E60</f>
+        <f>IF(COUNT(D60,E60)=2,D60*E60,NA())</f>
         <v>23902653000.0</v>
       </c>
       <c r="G60" s="2" t="s">
@@ -5196,7 +5202,7 @@
         <v>1000</v>
       </c>
       <c r="F61" s="3">
-        <f>D61*E61</f>
+        <f>IF(COUNT(D61,E61)=2,D61*E61,NA())</f>
         <v>13320128000.0</v>
       </c>
       <c r="G61" s="2" t="s">
@@ -5247,7 +5253,7 @@
         <v>1000</v>
       </c>
       <c r="F62" s="3">
-        <f>D62*E62</f>
+        <f>IF(COUNT(D62,E62)=2,D62*E62,NA())</f>
         <v>30728127000.0</v>
       </c>
       <c r="G62" s="2" t="s">
@@ -5298,7 +5304,7 @@
         <v>1000</v>
       </c>
       <c r="F63" s="3">
-        <f>D63*E63</f>
+        <f>IF(COUNT(D63,E63)=2,D63*E63,NA())</f>
         <v>2865508000.0</v>
       </c>
       <c r="G63" s="2" t="s">
@@ -5349,7 +5355,7 @@
         <v>1000</v>
       </c>
       <c r="F64" s="3">
-        <f>D64*E64</f>
+        <f>IF(COUNT(D64,E64)=2,D64*E64,NA())</f>
         <v>205516000.0</v>
       </c>
       <c r="G64" s="2" t="s">
@@ -5400,7 +5406,7 @@
         <v>1000</v>
       </c>
       <c r="F65" s="3">
-        <f>D65*E65</f>
+        <f>IF(COUNT(D65,E65)=2,D65*E65,NA())</f>
         <v>70414214000.0</v>
       </c>
       <c r="G65" s="2" t="s">
@@ -5453,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="3">
-        <f>D66*E66</f>
+        <f>IF(COUNT(D66,E66)=2,D66*E66,NA())</f>
         <v>661.0</v>
       </c>
       <c r="G66" s="2" t="s">
@@ -5506,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="3">
-        <f>D67*E67</f>
+        <f>IF(COUNT(D67,E67)=2,D67*E67,NA())</f>
         <v>475.0</v>
       </c>
       <c r="G67" s="2" t="s">
@@ -5559,7 +5565,7 @@
         <v>1000</v>
       </c>
       <c r="F68" s="3">
-        <f>D68*E68</f>
+        <f>IF(COUNT(D68,E68)=2,D68*E68,NA())</f>
         <v>8660164000.0</v>
       </c>
       <c r="G68" s="2" t="s">
@@ -5612,7 +5618,7 @@
         <v>1000</v>
       </c>
       <c r="F69" s="3">
-        <f>D69*E69</f>
+        <f>IF(COUNT(D69,E69)=2,D69*E69,NA())</f>
         <v>418585000.0</v>
       </c>
       <c r="G69" s="2" t="s">
@@ -5665,7 +5671,7 @@
         <v>1000</v>
       </c>
       <c r="F70" s="3">
-        <f>D70*E70</f>
+        <f>IF(COUNT(D70,E70)=2,D70*E70,NA())</f>
         <v>24322780000.0</v>
       </c>
       <c r="G70" s="2" t="s">
@@ -5718,7 +5724,7 @@
         <v>1000</v>
       </c>
       <c r="F71" s="3">
-        <f>D71*E71</f>
+        <f>IF(COUNT(D71,E71)=2,D71*E71,NA())</f>
         <v>337367000.0</v>
       </c>
       <c r="G71" s="2" t="s">
@@ -5771,7 +5777,7 @@
         <v>1000</v>
       </c>
       <c r="F72" s="3">
-        <f>D72*E72</f>
+        <f>IF(COUNT(D72,E72)=2,D72*E72,NA())</f>
         <v>512000000.0</v>
       </c>
       <c r="G72" s="2" t="s">
@@ -5824,7 +5830,7 @@
         <v>1000</v>
       </c>
       <c r="F73" s="3">
-        <f>D73*E73</f>
+        <f>IF(COUNT(D73,E73)=2,D73*E73,NA())</f>
         <v>1764508000.0</v>
       </c>
       <c r="G73" s="2" t="s">
@@ -5877,7 +5883,7 @@
         <v>1000</v>
       </c>
       <c r="F74" s="3">
-        <f>D74*E74</f>
+        <f>IF(COUNT(D74,E74)=2,D74*E74,NA())</f>
         <v>-174640000.0</v>
       </c>
       <c r="G74" s="2" t="s">
@@ -5930,7 +5936,7 @@
         <v>1000</v>
       </c>
       <c r="F75" s="3">
-        <f>D75*E75</f>
+        <f>IF(COUNT(D75,E75)=2,D75*E75,NA())</f>
         <v>151291000.0</v>
       </c>
       <c r="G75" s="2" t="s">
@@ -5983,7 +5989,7 @@
         <v>1000</v>
       </c>
       <c r="F76" s="3">
-        <f>D76*E76</f>
+        <f>IF(COUNT(D76,E76)=2,D76*E76,NA())</f>
         <v>-974079000.0</v>
       </c>
       <c r="G76" s="2" t="s">
@@ -6036,7 +6042,7 @@
         <v>1000</v>
       </c>
       <c r="F77" s="3">
-        <f>D77*E77</f>
+        <f>IF(COUNT(D77,E77)=2,D77*E77,NA())</f>
         <v>2470751000.0</v>
       </c>
       <c r="G77" s="2" t="s">
@@ -6089,7 +6095,7 @@
         <v>1000</v>
       </c>
       <c r="F78" s="3">
-        <f>D78*E78</f>
+        <f>IF(COUNT(D78,E78)=2,D78*E78,NA())</f>
         <v>-8429599000.0</v>
       </c>
       <c r="G78" s="2" t="s">
@@ -6142,7 +6148,7 @@
         <v>1000</v>
       </c>
       <c r="F79" s="3">
-        <f>D79*E79</f>
+        <f>IF(COUNT(D79,E79)=2,D79*E79,NA())</f>
         <v>-7660090000.0</v>
       </c>
       <c r="G79" s="2" t="s">
@@ -6195,7 +6201,7 @@
         <v>1000</v>
       </c>
       <c r="F80" s="3">
-        <f>D80*E80</f>
+        <f>IF(COUNT(D80,E80)=2,D80*E80,NA())</f>
         <v>1900952000.0</v>
       </c>
       <c r="G80" s="2" t="s">
@@ -6248,7 +6254,7 @@
         <v>1000</v>
       </c>
       <c r="F81" s="3">
-        <f>D81*E81</f>
+        <f>IF(COUNT(D81,E81)=2,D81*E81,NA())</f>
         <v>-39837988000.0</v>
       </c>
       <c r="G81" s="2" t="s">
@@ -6301,7 +6307,7 @@
         <v>1000</v>
       </c>
       <c r="F82" s="3">
-        <f>D82*E82</f>
+        <f>IF(COUNT(D82,E82)=2,D82*E82,NA())</f>
         <v>-16911542000.0</v>
       </c>
       <c r="G82" s="2" t="s">
@@ -6354,7 +6360,7 @@
         <v>1000</v>
       </c>
       <c r="F83" s="3">
-        <f>D83*E83</f>
+        <f>IF(COUNT(D83,E83)=2,D83*E83,NA())</f>
         <v>89965735000.0</v>
       </c>
       <c r="G83" s="2" t="s">
@@ -6407,7 +6413,7 @@
         <v>1000</v>
       </c>
       <c r="F84" s="3">
-        <f>D84*E84</f>
+        <f>IF(COUNT(D84,E84)=2,D84*E84,NA())</f>
         <v>-82524000.0</v>
       </c>
       <c r="G84" s="2" t="s">
@@ -6522,10 +6528,14 @@
         <f>D2/K2</f>
         <v>111318537.0</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G2" s="2"/>
+      <c r="F2" s="2" t="str">
+        <f>IF(ISNUMBER(D2),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G2" s="2">
+        <f>IF(ISNUMBER(D2),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H2" s="2" t="s">
         <v>239</v>
       </c>
@@ -6569,10 +6579,14 @@
         <f>D3/K3</f>
         <v>0.26272847570445024</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G3" s="2"/>
+      <c r="F3" s="2" t="str">
+        <f>IF(ISNUMBER(D3),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G3" s="2">
+        <f>IF(ISNUMBER(D3),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H3" s="2" t="s">
         <v>243</v>
       </c>
@@ -6616,10 +6630,14 @@
         <f>D4/K4</f>
         <v>0.1704064660696822</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G4" s="2"/>
+      <c r="F4" s="2" t="str">
+        <f>IF(ISNUMBER(D4),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G4" s="2">
+        <f>IF(ISNUMBER(D4),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H4" s="2" t="s">
         <v>247</v>
       </c>
@@ -6663,10 +6681,14 @@
         <f>D5/K5</f>
         <v>0.42178980296441965</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G5" s="2"/>
+      <c r="F5" s="2" t="str">
+        <f>IF(ISNUMBER(D5),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G5" s="2">
+        <f>IF(ISNUMBER(D5),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H5" s="2" t="s">
         <v>247</v>
       </c>
@@ -6710,10 +6732,14 @@
         <f>D6/K6</f>
         <v>0.3735385929393281</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G6" s="2"/>
+      <c r="F6" s="2" t="str">
+        <f>IF(ISNUMBER(D6),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G6" s="2">
+        <f>IF(ISNUMBER(D6),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H6" s="2" t="s">
         <v>247</v>
       </c>
@@ -6757,10 +6783,14 @@
         <f>D7/K7</f>
         <v>0.2508089498436376</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G7" s="2"/>
+      <c r="F7" s="2" t="str">
+        <f>IF(ISNUMBER(D7),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G7" s="2">
+        <f>IF(ISNUMBER(D7),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H7" s="2" t="s">
         <v>247</v>
       </c>
@@ -6804,10 +6834,14 @@
         <f>D8/K8</f>
         <v>0.0898816312523935</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="F8" s="2" t="str">
+        <f>IF(ISNUMBER(D8),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G8" s="2">
+        <f>IF(ISNUMBER(D8),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H8" s="2" t="s">
         <v>247</v>
       </c>
@@ -6851,10 +6885,14 @@
         <f>D9/K9</f>
         <v>-0.23829318777202804</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G9" s="2"/>
+      <c r="F9" s="2" t="str">
+        <f>IF(ISNUMBER(D9),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G9" s="2">
+        <f>IF(ISNUMBER(D9),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H9" s="2" t="s">
         <v>247</v>
       </c>
@@ -6898,10 +6936,14 @@
         <f>D10/K10</f>
         <v>0.391578947368421</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2" t="str">
+        <f>IF(ISNUMBER(D10),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G10" s="2">
+        <f>IF(ISNUMBER(D10),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H10" s="2" t="s">
         <v>247</v>
       </c>
@@ -6945,10 +6987,14 @@
         <f>D11/K11</f>
         <v>1.7349444677696384</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G11" s="2"/>
+      <c r="F11" s="2" t="str">
+        <f>IF(ISNUMBER(D11),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G11" s="2">
+        <f>IF(ISNUMBER(D11),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H11" s="2" t="s">
         <v>263</v>
       </c>
@@ -6992,10 +7038,14 @@
         <f>D12/K12</f>
         <v>133219980.0</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G12" s="2"/>
+      <c r="F12" s="2" t="str">
+        <f>IF(ISNUMBER(D12),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G12" s="2">
+        <f>IF(ISNUMBER(D12),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H12" s="2" t="s">
         <v>267</v>
       </c>
@@ -7039,10 +7089,14 @@
         <f>D13/K13</f>
         <v>33216205.0</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G13" s="2"/>
+      <c r="F13" s="2" t="str">
+        <f>IF(ISNUMBER(D13),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G13" s="2">
+        <f>IF(ISNUMBER(D13),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H13" s="2" t="s">
         <v>270</v>
       </c>
@@ -7086,10 +7140,14 @@
         <f>D14/K14</f>
         <v>90875424.0</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G14" s="2"/>
+      <c r="F14" s="2" t="str">
+        <f>IF(ISNUMBER(D14),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G14" s="2">
+        <f>IF(ISNUMBER(D14),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H14" s="2" t="s">
         <v>273</v>
       </c>
@@ -7133,10 +7191,14 @@
         <f>D15/K15</f>
         <v>29770009.0</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G15" s="2"/>
+      <c r="F15" s="2" t="str">
+        <f>IF(ISNUMBER(D15),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G15" s="2">
+        <f>IF(ISNUMBER(D15),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H15" s="2" t="s">
         <v>277</v>
       </c>
@@ -7180,10 +7242,14 @@
         <f>D16/K16</f>
         <v>299929743.0</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G16" s="2"/>
+      <c r="F16" s="2" t="str">
+        <f>IF(ISNUMBER(D16),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G16" s="2">
+        <f>IF(ISNUMBER(D16),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H16" s="2" t="s">
         <v>280</v>
       </c>
@@ -7227,10 +7293,14 @@
         <f>D17/K17</f>
         <v>974827544.0</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G17" s="2"/>
+      <c r="F17" s="2" t="str">
+        <f>IF(ISNUMBER(D17),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G17" s="2">
+        <f>IF(ISNUMBER(D17),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H17" s="2" t="s">
         <v>283</v>
       </c>
@@ -7272,10 +7342,14 @@
         <f>D18/K18</f>
         <v>76786309.0</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G18" s="2"/>
+      <c r="F18" s="2" t="str">
+        <f>IF(ISNUMBER(D18),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G18" s="2">
+        <f>IF(ISNUMBER(D18),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H18" s="2" t="s">
         <v>286</v>
       </c>
@@ -7319,10 +7393,14 @@
         <f>D19/K19</f>
         <v>371026323.0</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G19" s="2"/>
+      <c r="F19" s="2" t="str">
+        <f>IF(ISNUMBER(D19),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G19" s="2">
+        <f>IF(ISNUMBER(D19),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H19" s="2" t="s">
         <v>289</v>
       </c>
@@ -7366,10 +7444,14 @@
         <f>D20/K20</f>
         <v>119601197.0</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G20" s="2"/>
+      <c r="F20" s="2" t="str">
+        <f>IF(ISNUMBER(D20),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G20" s="2">
+        <f>IF(ISNUMBER(D20),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H20" s="2" t="s">
         <v>292</v>
       </c>
@@ -7413,10 +7495,14 @@
         <f>D21/K21</f>
         <v>37222781.0</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G21" s="2"/>
+      <c r="F21" s="2" t="str">
+        <f>IF(ISNUMBER(D21),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G21" s="2">
+        <f>IF(ISNUMBER(D21),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H21" s="2" t="s">
         <v>295</v>
       </c>
@@ -7458,10 +7544,14 @@
         <f>D22/K22</f>
         <v>-7139628.0</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G22" s="2"/>
+      <c r="F22" s="2" t="str">
+        <f>IF(ISNUMBER(D22),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G22" s="2">
+        <f>IF(ISNUMBER(D22),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H22" s="2" t="s">
         <v>298</v>
       </c>
@@ -7503,10 +7593,14 @@
         <f>D23/K23</f>
         <v>333512926.0</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G23" s="2"/>
+      <c r="F23" s="2" t="str">
+        <f>IF(ISNUMBER(D23),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G23" s="2">
+        <f>IF(ISNUMBER(D23),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H23" s="2" t="s">
         <v>301</v>
       </c>
@@ -7548,10 +7642,14 @@
         <f>D24/K24</f>
         <v>33583186.0</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G24" s="2"/>
+      <c r="F24" s="2" t="str">
+        <f>IF(ISNUMBER(D24),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G24" s="2">
+        <f>IF(ISNUMBER(D24),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H24" s="2" t="s">
         <v>304</v>
       </c>
@@ -7593,10 +7691,14 @@
         <f>D25/K25</f>
         <v>156823978.0</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G25" s="2"/>
+      <c r="F25" s="2" t="str">
+        <f>IF(ISNUMBER(D25),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G25" s="2">
+        <f>IF(ISNUMBER(D25),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H25" s="2" t="s">
         <v>307</v>
       </c>
@@ -7638,10 +7740,14 @@
         <f>D26/K26</f>
         <v>292018890.0</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G26" s="2"/>
+      <c r="F26" s="2" t="str">
+        <f>IF(ISNUMBER(D26),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G26" s="2">
+        <f>IF(ISNUMBER(D26),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H26" s="2" t="s">
         <v>311</v>
       </c>
@@ -7685,10 +7791,14 @@
         <f>D27/K27</f>
         <v>0.24724866942683058</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G27" s="2"/>
+      <c r="F27" s="2" t="str">
+        <f>IF(ISNUMBER(D27),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G27" s="2">
+        <f>IF(ISNUMBER(D27),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H27" s="2" t="s">
         <v>314</v>
       </c>
@@ -7732,10 +7842,14 @@
         <f>D28/K28</f>
         <v>2659992.0</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G28" s="2"/>
+      <c r="F28" s="2" t="str">
+        <f>IF(ISNUMBER(D28),"calculated","not_calculated")</f>
+        <v>calculated</v>
+      </c>
+      <c r="G28" s="2">
+        <f>IF(ISNUMBER(D28),"","检查缺失值、分母与输入；口径变更须重跑Python")</f>
+        <v/>
+      </c>
       <c r="H28" s="2" t="s">
         <v>318</v>
       </c>
@@ -7767,13 +7881,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="28.7109375" customWidth="1"/>
+    <col min="1" max="9" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32" customHeight="1">
+    <row r="1" spans="1:9" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -7798,13 +7912,16 @@
       <c r="H1" s="1" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>281</v>
@@ -7819,19 +7936,24 @@
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>355</v>
+      <c r="G2" s="2" t="str">
+        <f>IF(COUNT(E2,F2)&lt;2,"not_tested",IF(ABS(E2)&lt;=F2,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I2" s="2">
+        <f>IF(ISNUMBER(E2),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>284</v>
@@ -7846,19 +7968,24 @@
       <c r="F3" s="2">
         <v>1000</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>355</v>
+      <c r="G3" s="2" t="str">
+        <f>IF(COUNT(E3,F3)&lt;2,"not_tested",IF(ABS(E3)&lt;=F3,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I3" s="2">
+        <f>IF(ISNUMBER(E3),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>265</v>
@@ -7873,19 +8000,24 @@
       <c r="F4" s="2">
         <v>10000</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>355</v>
+      <c r="G4" s="2" t="str">
+        <f>IF(COUNT(E4,F4)&lt;2,"not_tested",IF(ABS(E4)&lt;=F4,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I4" s="2">
+        <f>IF(ISNUMBER(E4),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>275</v>
@@ -7900,19 +8032,24 @@
       <c r="F5" s="2">
         <v>2000</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>355</v>
+      <c r="G5" s="2" t="str">
+        <f>IF(COUNT(E5,F5)&lt;2,"not_tested",IF(ABS(E5)&lt;=F5,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I5" s="2">
+        <f>IF(ISNUMBER(E5),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>278</v>
@@ -7927,19 +8064,24 @@
       <c r="F6" s="2">
         <v>3000</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>355</v>
+      <c r="G6" s="2" t="str">
+        <f>IF(COUNT(E6,F6)&lt;2,"not_tested",IF(ABS(E6)&lt;=F6,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I6" s="2">
+        <f>IF(ISNUMBER(E6),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>287</v>
@@ -7954,19 +8096,24 @@
       <c r="F7" s="2">
         <v>3000</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>355</v>
+      <c r="G7" s="2" t="str">
+        <f>IF(COUNT(E7,F7)&lt;2,"not_tested",IF(ABS(E7)&lt;=F7,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I7" s="2">
+        <f>IF(ISNUMBER(E7),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>290</v>
@@ -7981,19 +8128,24 @@
       <c r="F8" s="2">
         <v>3000</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>355</v>
+      <c r="G8" s="2" t="str">
+        <f>IF(COUNT(E8,F8)&lt;2,"not_tested",IF(ABS(E8)&lt;=F8,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I8" s="2">
+        <f>IF(ISNUMBER(E8),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>293</v>
@@ -8008,19 +8160,24 @@
       <c r="F9" s="2">
         <v>1000</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>355</v>
+      <c r="G9" s="2" t="str">
+        <f>IF(COUNT(E9,F9)&lt;2,"not_tested",IF(ABS(E9)&lt;=F9,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I9" s="2">
+        <f>IF(ISNUMBER(E9),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>299</v>
@@ -8035,19 +8192,24 @@
       <c r="F10" s="2">
         <v>2000</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>355</v>
+      <c r="G10" s="2" t="str">
+        <f>IF(COUNT(E10,F10)&lt;2,"not_tested",IF(ABS(E10)&lt;=F10,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>357</v>
+      </c>
+      <c r="I10" s="2">
+        <f>IF(ISNUMBER(E10),"","missing or unavailable input")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>302</v>
@@ -8062,67 +8224,76 @@
       <c r="F11" s="2">
         <v>2000</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>355</v>
+      <c r="G11" s="2" t="str">
+        <f>IF(COUNT(E11,F11)&lt;2,"not_tested",IF(ABS(E11)&lt;=F11,"within_input_tolerance","unexplained_difference"))</f>
+        <v>within_input_tolerance</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
+      </c>
+      <c r="I11" s="2">
+        <f>IF(ISNUMBER(E11),"","missing or unavailable input")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:I11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" customWidth="1"/>
     <col min="3" max="3" width="100.7109375" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="70.7109375" customWidth="1"/>
+    <col min="5" max="6" width="70.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
+    <row r="1" spans="1:6" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>379</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>382</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="F2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:F2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8143,16 +8314,16 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8160,16 +8331,16 @@
         <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8177,16 +8348,16 @@
         <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8194,16 +8365,16 @@
         <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8211,16 +8382,16 @@
         <v>63</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8228,33 +8399,33 @@
         <v>145</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8262,16 +8433,16 @@
         <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8279,16 +8450,16 @@
         <v>113</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8296,16 +8467,16 @@
         <v>103</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8313,16 +8484,16 @@
         <v>68</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8330,16 +8501,16 @@
         <v>160</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8347,33 +8518,33 @@
         <v>108</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -8401,223 +8572,223 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>118</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -8639,93 +8810,93 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -8751,59 +8922,59 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>

--- a/examples/catl-2025/deliverables/workbook.xlsx
+++ b/examples/catl-2025/deliverables/workbook.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Facts!$A$1:$R$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Findings!$A$1:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Procedures!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Readme!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reconciliations!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Readme!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reconciliations!$A$1:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Requests!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sources!$A$1:$F$2</definedName>
   </definedNames>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="517">
   <si>
     <t>字段 / field</t>
   </si>
@@ -83,6 +83,12 @@
     <t>数值公式可编辑；修改主体、期间、币种、规则或资料后须重跑 export.py 复核口径。</t>
   </si>
   <si>
+    <t>勾稽精度</t>
+  </si>
+  <si>
+    <t>金额残差按本次Decimal输入/计算保留的小数位ROUND，消除Excel二进制尾差，不改变业务容差；提高输入小数精度后须重跑导出。</t>
+  </si>
+  <si>
     <t>缺口</t>
   </si>
   <si>
@@ -1095,6 +1101,9 @@
   </si>
   <si>
     <t>未测试原因</t>
+  </si>
+  <si>
+    <t>金额残差小数位</t>
   </si>
   <si>
     <t>R_BS</t>
@@ -1943,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -2032,22 +2041,30 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2062,69 +2079,69 @@
   <sheetData>
     <row r="1" spans="1:18" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2">
         <v>423701834</v>
@@ -2137,47 +2154,47 @@
         <v>423701834000.0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2">
         <v>362012554</v>
@@ -2190,47 +2207,47 @@
         <v>362012554000.0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2">
         <v>312383297</v>
@@ -2243,47 +2260,47 @@
         <v>312383297000.0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R4" s="2"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2">
         <v>273518959</v>
@@ -2296,47 +2313,47 @@
         <v>273518959000.0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2">
         <v>76786309</v>
@@ -2349,47 +2366,47 @@
         <v>76786309000.0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D7" s="2">
         <v>54006794</v>
@@ -2402,47 +2419,47 @@
         <v>54006794000.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2">
         <v>133219982</v>
@@ -2455,47 +2472,47 @@
         <v>133219982000.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="D9" s="2">
         <v>96990345</v>
@@ -2508,47 +2525,47 @@
         <v>96990345000.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D10" s="2">
         <v>299929741</v>
@@ -2561,45 +2578,45 @@
         <v>299929741000.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="D11" s="2">
         <v>270159734</v>
@@ -2612,45 +2629,45 @@
         <v>270159734000.0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2">
         <v>974827544</v>
@@ -2663,45 +2680,45 @@
         <v>974827544000.0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D13" s="2">
         <v>786658123</v>
@@ -2714,45 +2731,45 @@
         <v>786658123000.0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2">
         <v>371026324</v>
@@ -2765,45 +2782,45 @@
         <v>371026324000.0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2">
         <v>273456174</v>
@@ -2816,45 +2833,45 @@
         <v>273456174000.0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2">
         <v>337107747</v>
@@ -2867,45 +2884,45 @@
         <v>337107747000.0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2">
         <v>246930033</v>
@@ -2918,45 +2935,45 @@
         <v>246930033000.0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R17" s="2"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2">
         <v>94526239</v>
@@ -2969,45 +2986,45 @@
         <v>94526239000.0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2">
         <v>59835533</v>
@@ -3020,45 +3037,45 @@
         <v>59835533000.0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2">
         <v>76403264</v>
@@ -3071,45 +3088,45 @@
         <v>76403264000.0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R20" s="2"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2">
         <v>64135510</v>
@@ -3122,45 +3139,45 @@
         <v>64135510000.0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R21" s="2"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2">
         <v>160328962</v>
@@ -3173,45 +3190,45 @@
         <v>160328962000.0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R22" s="2"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2">
         <v>130977408</v>
@@ -3224,45 +3241,45 @@
         <v>130977408000.0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R23" s="2"/>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2">
         <v>49233377</v>
@@ -3275,45 +3292,45 @@
         <v>49233377000.0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D25" s="2">
         <v>27834446</v>
@@ -3326,45 +3343,45 @@
         <v>27834446000.0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R25" s="2"/>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D26" s="2">
         <v>37222781</v>
@@ -3377,45 +3394,45 @@
         <v>37222781000.0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R26" s="2"/>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="D27" s="2">
         <v>44362409</v>
@@ -3428,45 +3445,45 @@
         <v>44362409000.0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R27" s="2"/>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D28" s="2">
         <v>51233080</v>
@@ -3479,45 +3496,45 @@
         <v>51233080000.0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="R28" s="2"/>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D29" s="2">
         <v>39070181</v>
@@ -3530,45 +3547,45 @@
         <v>39070181000.0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="R29" s="2"/>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D30" s="2">
         <v>119601197</v>
@@ -3581,45 +3598,45 @@
         <v>119601197000.0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R30" s="2"/>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="D31" s="2">
         <v>136346553</v>
@@ -3632,45 +3649,45 @@
         <v>136346553000.0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R31" s="2"/>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D32" s="2">
         <v>316506369</v>
@@ -3683,47 +3700,47 @@
         <v>316506369000.0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R32" s="2"/>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="D33" s="2">
         <v>253041337</v>
@@ -3736,47 +3753,47 @@
         <v>253041337000.0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D34" s="2">
         <v>62439820</v>
@@ -3789,47 +3806,47 @@
         <v>62439820000.0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R34" s="2"/>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D35" s="2">
         <v>57290460</v>
@@ -3842,47 +3859,47 @@
         <v>57290460000.0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R35" s="2"/>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D36" s="2">
         <v>21860936</v>
@@ -3895,47 +3912,47 @@
         <v>21860936000.0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R36" s="2"/>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D37" s="2">
         <v>28699935</v>
@@ -3948,47 +3965,47 @@
         <v>28699935000.0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R37" s="2"/>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2">
         <v>72201282</v>
@@ -4001,47 +4018,47 @@
         <v>72201282000.0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="R38" s="2"/>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2">
         <v>4585027</v>
@@ -4054,47 +4071,47 @@
         <v>4585027000.0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R39" s="2"/>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D40" s="2">
         <v>-94475790</v>
@@ -4107,47 +4124,47 @@
         <v>-94475790000.0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="R40" s="2"/>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D41" s="2">
         <v>-6309543</v>
@@ -4160,47 +4177,47 @@
         <v>-6309543000.0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="R41" s="2"/>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D42" s="2">
         <v>-2664640</v>
@@ -4213,47 +4230,47 @@
         <v>-2664640000.0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="R42" s="2"/>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D43" s="2">
         <v>29770008</v>
@@ -4266,47 +4283,47 @@
         <v>29770008000.0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="R43" s="2"/>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D44" s="2">
         <v>42344558</v>
@@ -4319,47 +4336,47 @@
         <v>42344558000.0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R44" s="2"/>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D45" s="2">
         <v>84006523</v>
@@ -4372,47 +4389,47 @@
         <v>84006523000.0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R45" s="2"/>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="D46" s="2">
         <v>40416391</v>
@@ -4425,47 +4442,47 @@
         <v>40416391000.0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R46" s="2"/>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D47" s="2">
         <v>-26842954</v>
@@ -4478,47 +4495,47 @@
         <v>-26842954000.0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="R47" s="2"/>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D48" s="2">
         <v>-9811</v>
@@ -4531,47 +4548,47 @@
         <v>-9811000.0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R48" s="2"/>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D49" s="2">
         <v>39790079</v>
@@ -4584,47 +4601,47 @@
         <v>39790079000.0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="R49" s="2"/>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D50" s="2">
         <v>-54608510</v>
@@ -4637,47 +4654,47 @@
         <v>-54608510000.0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R50" s="2"/>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D51" s="2">
         <v>-1926925</v>
@@ -4690,47 +4707,47 @@
         <v>-1926925000.0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R51" s="2"/>
     </row>
     <row r="52" spans="1:18">
       <c r="A52" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D52" s="2">
         <v>2659992</v>
@@ -4743,47 +4760,47 @@
         <v>2659992000.0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R52" s="2"/>
     </row>
     <row r="53" spans="1:18">
       <c r="A53" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D53" s="2">
         <v>60616240</v>
@@ -4796,47 +4813,47 @@
         <v>60616240000.0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R53" s="2"/>
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D54" s="2">
         <v>603801220</v>
@@ -4849,45 +4866,45 @@
         <v>603801220000.0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R54" s="2"/>
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D55" s="2">
         <v>333512927</v>
@@ -4900,45 +4917,45 @@
         <v>333512927000.0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="R55" s="2"/>
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D56" s="2">
         <v>33583185</v>
@@ -4951,45 +4968,45 @@
         <v>33583185000.0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P56" s="2"/>
       <c r="Q56" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="R56" s="2"/>
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2">
         <v>18428631</v>
@@ -5002,45 +5019,45 @@
         <v>18428631000.0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="R57" s="2"/>
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D58" s="2">
         <v>461587</v>
@@ -5053,45 +5070,45 @@
         <v>461587000.0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R58" s="2"/>
     </row>
     <row r="59" spans="1:18">
       <c r="A59" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D59" s="2">
         <v>14692968</v>
@@ -5104,45 +5121,45 @@
         <v>14692968000.0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="R59" s="2"/>
     </row>
     <row r="60" spans="1:18">
       <c r="A60" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D60" s="2">
         <v>23902653</v>
@@ -5155,45 +5172,45 @@
         <v>23902653000.0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="R60" s="2"/>
     </row>
     <row r="61" spans="1:18">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D61" s="2">
         <v>13320128</v>
@@ -5206,45 +5223,45 @@
         <v>13320128000.0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R61" s="2"/>
     </row>
     <row r="62" spans="1:18">
       <c r="A62" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D62" s="2">
         <v>30728127</v>
@@ -5257,45 +5274,45 @@
         <v>30728127000.0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="R62" s="2"/>
     </row>
     <row r="63" spans="1:18">
       <c r="A63" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D63" s="2">
         <v>2865508</v>
@@ -5308,45 +5325,45 @@
         <v>2865508000.0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="R63" s="2"/>
     </row>
     <row r="64" spans="1:18">
       <c r="A64" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D64" s="2">
         <v>205516</v>
@@ -5359,45 +5376,45 @@
         <v>205516000.0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="R64" s="2"/>
     </row>
     <row r="65" spans="1:18">
       <c r="A65" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D65" s="2">
         <v>70414214</v>
@@ -5410,47 +5427,47 @@
         <v>70414214000.0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P65" s="2"/>
       <c r="Q65" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="R65" s="2"/>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D66" s="2">
         <v>661</v>
@@ -5463,47 +5480,47 @@
         <v>661.0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:18">
       <c r="A67" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D67" s="2">
         <v>475</v>
@@ -5516,47 +5533,47 @@
         <v>475.0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D68" s="2">
         <v>8660164</v>
@@ -5569,47 +5586,47 @@
         <v>8660164000.0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="R68" s="2"/>
     </row>
     <row r="69" spans="1:18">
       <c r="A69" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D69" s="2">
         <v>418585</v>
@@ -5622,47 +5639,47 @@
         <v>418585000.0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="R69" s="2"/>
     </row>
     <row r="70" spans="1:18">
       <c r="A70" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D70" s="2">
         <v>24322780</v>
@@ -5675,47 +5692,47 @@
         <v>24322780000.0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R70" s="2"/>
     </row>
     <row r="71" spans="1:18">
       <c r="A71" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D71" s="2">
         <v>337367</v>
@@ -5728,47 +5745,47 @@
         <v>337367000.0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R71" s="2"/>
     </row>
     <row r="72" spans="1:18">
       <c r="A72" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D72" s="2">
         <v>512000</v>
@@ -5781,47 +5798,47 @@
         <v>512000000.0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="R72" s="2"/>
     </row>
     <row r="73" spans="1:18">
       <c r="A73" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D73" s="2">
         <v>1764508</v>
@@ -5834,47 +5851,47 @@
         <v>1764508000.0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="R73" s="2"/>
     </row>
     <row r="74" spans="1:18">
       <c r="A74" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D74" s="2">
         <v>-174640</v>
@@ -5887,47 +5904,47 @@
         <v>-174640000.0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R74" s="2"/>
     </row>
     <row r="75" spans="1:18">
       <c r="A75" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D75" s="2">
         <v>151291</v>
@@ -5940,47 +5957,47 @@
         <v>151291000.0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="R75" s="2"/>
     </row>
     <row r="76" spans="1:18">
       <c r="A76" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D76" s="2">
         <v>-974079</v>
@@ -5993,47 +6010,47 @@
         <v>-974079000.0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="R76" s="2"/>
     </row>
     <row r="77" spans="1:18">
       <c r="A77" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D77" s="2">
         <v>2470751</v>
@@ -6046,47 +6063,47 @@
         <v>2470751000.0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="R77" s="2"/>
     </row>
     <row r="78" spans="1:18">
       <c r="A78" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D78" s="2">
         <v>-8429599</v>
@@ -6099,47 +6116,47 @@
         <v>-8429599000.0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P78" s="2"/>
       <c r="Q78" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="R78" s="2"/>
     </row>
     <row r="79" spans="1:18">
       <c r="A79" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D79" s="2">
         <v>-7660090</v>
@@ -6152,47 +6169,47 @@
         <v>-7660090000.0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P79" s="2"/>
       <c r="Q79" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="R79" s="2"/>
     </row>
     <row r="80" spans="1:18">
       <c r="A80" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D80" s="2">
         <v>1900952</v>
@@ -6205,47 +6222,47 @@
         <v>1900952000.0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R80" s="2"/>
     </row>
     <row r="81" spans="1:18">
       <c r="A81" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D81" s="2">
         <v>-39837988</v>
@@ -6258,47 +6275,47 @@
         <v>-39837988000.0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R81" s="2"/>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D82" s="2">
         <v>-16911542</v>
@@ -6311,47 +6328,47 @@
         <v>-16911542000.0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="R82" s="2"/>
     </row>
     <row r="83" spans="1:18">
       <c r="A83" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D83" s="2">
         <v>89965735</v>
@@ -6364,47 +6381,47 @@
         <v>89965735000.0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R83" s="2"/>
     </row>
     <row r="84" spans="1:18">
       <c r="A84" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D84" s="2">
         <v>-82524</v>
@@ -6417,35 +6434,35 @@
         <v>-82524000.0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P84" s="2"/>
       <c r="Q84" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="R84" s="2"/>
     </row>
@@ -6465,60 +6482,60 @@
   <sheetData>
     <row r="1" spans="1:15" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D2" s="3">
         <f>(('Facts'!F2-'Facts'!F4))*1</f>
@@ -6537,39 +6554,39 @@
         <v/>
       </c>
       <c r="H2" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K2" s="2">
         <v>1000</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D3" s="3">
         <f>IF('Facts'!F2&lt;=0,NA(),(('Calculations'!D2/'Facts'!F2))*1)</f>
@@ -6588,39 +6605,39 @@
         <v/>
       </c>
       <c r="H3" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D4" s="3">
         <f>IF(OR('Facts'!F3&lt;=0,'Facts'!F2&lt;0),NA(),((('Facts'!F2-'Facts'!F3)/'Facts'!F3))*1)</f>
@@ -6639,39 +6656,39 @@
         <v/>
       </c>
       <c r="H4" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D5" s="3">
         <f>IF(OR('Facts'!F7&lt;=0,'Facts'!F6&lt;0),NA(),((('Facts'!F6-'Facts'!F7)/'Facts'!F7))*1)</f>
@@ -6690,39 +6707,39 @@
         <v/>
       </c>
       <c r="H5" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D6" s="3">
         <f>IF(OR('Facts'!F9&lt;=0,'Facts'!F8&lt;0),NA(),((('Facts'!F8-'Facts'!F9)/'Facts'!F9))*1)</f>
@@ -6741,39 +6758,39 @@
         <v/>
       </c>
       <c r="H6" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D7" s="3">
         <f>IF(OR('Facts'!F33&lt;=0,'Facts'!F32&lt;0),NA(),((('Facts'!F32-'Facts'!F33)/'Facts'!F33))*1)</f>
@@ -6792,39 +6809,39 @@
         <v/>
       </c>
       <c r="H7" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D8" s="3">
         <f>IF(OR('Facts'!F35&lt;=0,'Facts'!F34&lt;0),NA(),((('Facts'!F34-'Facts'!F35)/'Facts'!F35))*1)</f>
@@ -6843,39 +6860,39 @@
         <v/>
       </c>
       <c r="H8" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D9" s="3">
         <f>IF(OR('Facts'!F37&lt;=0,'Facts'!F36&lt;0),NA(),((('Facts'!F36-'Facts'!F37)/'Facts'!F37))*1)</f>
@@ -6894,39 +6911,39 @@
         <v/>
       </c>
       <c r="H9" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D10" s="3">
         <f>IF(OR('Facts'!F67&lt;=0,'Facts'!F66&lt;0),NA(),((('Facts'!F66-'Facts'!F67)/'Facts'!F67))*1)</f>
@@ -6945,39 +6962,39 @@
         <v/>
       </c>
       <c r="H10" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D11" s="3">
         <f>IF('Facts'!F6&lt;=0,NA(),(('Facts'!F8/'Facts'!F6))*1)</f>
@@ -6996,39 +7013,39 @@
         <v/>
       </c>
       <c r="H11" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D12" s="3">
         <f>(('Facts'!F6*1)+('Facts'!F68*1)+('Facts'!F69*1)+('Facts'!F70*1)+('Facts'!F71*1)+('Facts'!F72*1)+('Facts'!F73*1)+('Facts'!F74*1)+('Facts'!F75*1)+('Facts'!F76*1)+('Facts'!F77*1)+('Facts'!F78*1)+('Facts'!F79*1)+('Facts'!F80*1)+('Facts'!F81*1)+('Facts'!F82*1)+('Facts'!F83*1)+('Facts'!F84*1))*1</f>
@@ -7047,39 +7064,39 @@
         <v/>
       </c>
       <c r="H12" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K12" s="2">
         <v>1000</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D13" s="3">
         <f>(('Facts'!F81*1)+('Facts'!F82*1)+('Facts'!F83*1))*1</f>
@@ -7098,39 +7115,39 @@
         <v/>
       </c>
       <c r="H13" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K13" s="2">
         <v>1000</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D14" s="3">
         <f>(('Facts'!F8-'Facts'!F44))*1</f>
@@ -7149,39 +7166,39 @@
         <v/>
       </c>
       <c r="H14" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K14" s="2">
         <v>1000</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D15" s="3">
         <f>(('Facts'!F8*1)+('Facts'!F40*1)+('Facts'!F41*1)+('Facts'!F42*1))*1</f>
@@ -7200,39 +7217,39 @@
         <v/>
       </c>
       <c r="H15" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K15" s="2">
         <v>1000</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D16" s="3">
         <f>(('Facts'!F11*1)+('Facts'!F8*1)+('Facts'!F40*1)+('Facts'!F41*1)+('Facts'!F42*1))*1</f>
@@ -7251,39 +7268,39 @@
         <v/>
       </c>
       <c r="H16" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K16" s="2">
         <v>1000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D17" s="3">
         <f>(('Facts'!F54*1)+('Facts'!F14*1))*1</f>
@@ -7302,37 +7319,37 @@
         <v/>
       </c>
       <c r="H17" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K17" s="2">
         <v>1000</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D18" s="3">
         <f>(('Facts'!F38*1)+('Facts'!F39*1))*1</f>
@@ -7351,39 +7368,39 @@
         <v/>
       </c>
       <c r="H18" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K18" s="2">
         <v>1000</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D19" s="3">
         <f>(('Facts'!F15*1)+('Facts'!F45*1)+('Facts'!F46*1)+('Facts'!F47*1)+('Facts'!F48*1))*1</f>
@@ -7402,39 +7419,39 @@
         <v/>
       </c>
       <c r="H19" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K19" s="2">
         <v>1000</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D20" s="3">
         <f>(('Facts'!F31*1)+('Facts'!F49*1)+('Facts'!F50*1)+('Facts'!F51*1))*1</f>
@@ -7453,39 +7470,39 @@
         <v/>
       </c>
       <c r="H20" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K20" s="2">
         <v>1000</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D21" s="3">
         <f>(('Facts'!F60*1)+('Facts'!F61*1))*1</f>
@@ -7504,37 +7521,37 @@
         <v/>
       </c>
       <c r="H21" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K21" s="2">
         <v>1000</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D22" s="3">
         <f>(('Facts'!F26-'Facts'!F27))*1</f>
@@ -7553,37 +7570,37 @@
         <v/>
       </c>
       <c r="H22" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K22" s="2">
         <v>1000</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D23" s="3">
         <f>(('Facts'!F10*1)+('Facts'!F56*1))*1</f>
@@ -7602,37 +7619,37 @@
         <v/>
       </c>
       <c r="H23" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K23" s="2">
         <v>1000</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D24" s="3">
         <f>(('Facts'!F57*1)+('Facts'!F58*1)+('Facts'!F59*1))*1</f>
@@ -7651,37 +7668,37 @@
         <v/>
       </c>
       <c r="H24" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K24" s="2">
         <v>1000</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D25" s="3">
         <f>(('Facts'!F30*1)+('Facts'!F26*1))*1</f>
@@ -7700,37 +7717,37 @@
         <v/>
       </c>
       <c r="H25" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K25" s="2">
         <v>1000</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D26" s="3">
         <f>(AVERAGE('Facts'!F17,'Facts'!F16))*1</f>
@@ -7749,39 +7766,39 @@
         <v/>
       </c>
       <c r="H26" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K26" s="2">
         <v>1000</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D27" s="3">
         <f>IF('Calculations'!D26&lt;=0,NA(),(('Facts'!F38/'Calculations'!D26))*1)</f>
@@ -7800,39 +7817,39 @@
         <v/>
       </c>
       <c r="H27" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D28" s="3">
         <f>(('Facts'!F63-'Facts'!F64))*1</f>
@@ -7851,26 +7868,26 @@
         <v/>
       </c>
       <c r="H28" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K28" s="2">
         <v>1000</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -7881,56 +7898,59 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="28.7109375" customWidth="1"/>
+    <col min="1" max="10" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32" customHeight="1">
+    <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>355</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E2" s="3">
-        <f>'Calculations'!D17-'Facts'!F12</f>
+        <f>ROUND('Calculations'!D17-'Facts'!F12,J2)</f>
         <v>0.0</v>
       </c>
       <c r="F2" s="2">
@@ -7941,28 +7961,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I2" s="2">
         <f>IF(ISNUMBER(E2),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3">
-        <f>'Calculations'!D18-'Facts'!F6</f>
+        <f>ROUND('Calculations'!D18-'Facts'!F6,J3)</f>
         <v>0.0</v>
       </c>
       <c r="F3" s="2">
@@ -7973,28 +7996,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I3" s="2">
         <f>IF(ISNUMBER(E3),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E4" s="3">
-        <f>'Calculations'!D12-'Facts'!F8</f>
+        <f>ROUND('Calculations'!D12-'Facts'!F8,J4)</f>
         <v>-2000.0</v>
       </c>
       <c r="F4" s="2">
@@ -8005,28 +8031,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I4" s="2">
         <f>IF(ISNUMBER(E4),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5" s="3">
-        <f>'Calculations'!D15-'Facts'!F43</f>
+        <f>ROUND('Calculations'!D15-'Facts'!F43,J5)</f>
         <v>1000.0</v>
       </c>
       <c r="F5" s="2">
@@ -8037,28 +8066,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I5" s="2">
         <f>IF(ISNUMBER(E5),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3">
-        <f>'Calculations'!D16-'Facts'!F10</f>
+        <f>ROUND('Calculations'!D16-'Facts'!F10,J6)</f>
         <v>2000.0</v>
       </c>
       <c r="F6" s="2">
@@ -8069,28 +8101,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I6" s="2">
         <f>IF(ISNUMBER(E6),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E7" s="3">
-        <f>'Calculations'!D19-'Facts'!F14</f>
+        <f>ROUND('Calculations'!D19-'Facts'!F14,J7)</f>
         <v>-1000.0</v>
       </c>
       <c r="F7" s="2">
@@ -8101,28 +8136,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I7" s="2">
         <f>IF(ISNUMBER(E7),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E8" s="3">
-        <f>'Calculations'!D20-'Facts'!F30</f>
+        <f>ROUND('Calculations'!D20-'Facts'!F30,J8)</f>
         <v>0.0</v>
       </c>
       <c r="F8" s="2">
@@ -8133,28 +8171,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I8" s="2">
         <f>IF(ISNUMBER(E8),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E9" s="3">
-        <f>'Calculations'!D21-'Facts'!F26</f>
+        <f>ROUND('Calculations'!D21-'Facts'!F26,J9)</f>
         <v>0.0</v>
       </c>
       <c r="F9" s="2">
@@ -8165,28 +8206,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I9" s="2">
         <f>IF(ISNUMBER(E9),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E10" s="3">
-        <f>'Calculations'!D23-'Facts'!F55</f>
+        <f>ROUND('Calculations'!D23-'Facts'!F55,J10)</f>
         <v>-1000.0</v>
       </c>
       <c r="F10" s="2">
@@ -8197,28 +8241,31 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I10" s="2">
         <f>IF(ISNUMBER(E10),"","missing or unavailable input")</f>
         <v/>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E11" s="3">
-        <f>'Calculations'!D24-'Facts'!F56</f>
+        <f>ROUND('Calculations'!D24-'Facts'!F56,J11)</f>
         <v>1000.0</v>
       </c>
       <c r="F11" s="2">
@@ -8229,15 +8276,18 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I11" s="2">
         <f>IF(ISNUMBER(E11),"","missing or unavailable input")</f>
         <v/>
       </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
+  <autoFilter ref="A1:J11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8256,39 +8306,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -8311,240 +8361,240 @@
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -8569,226 +8619,226 @@
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -8807,96 +8857,96 @@
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -8919,62 +8969,62 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>

--- a/examples/catl-2025/deliverables/workbook.xlsx
+++ b/examples/catl-2025/deliverables/workbook.xlsx
@@ -23,17 +23,20 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Facts!$A$1:$R$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Findings!$A$1:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Procedures!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Readme!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Readme!$A$1:$B$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reconciliations!$A$1:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Requests!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sources!$A$1:$F$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">Calculations!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Readme!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">Reconciliations!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="519">
   <si>
     <t>字段 / field</t>
   </si>
@@ -71,6 +74,12 @@
     <t>CAS</t>
   </si>
   <si>
+    <t>方法与适用范围</t>
+  </si>
+  <si>
+    <t>年报四表及附注复算；分析者明确口径的供应商融资敏感性</t>
+  </si>
+  <si>
     <t>单位</t>
   </si>
   <si>
@@ -773,7 +782,7 @@
     <t>毛利/营业收入</t>
   </si>
   <si>
-    <t>ratio</t>
+    <t>%</t>
   </si>
   <si>
     <t>revenue_growth</t>
@@ -1375,7 +1384,7 @@
     <t>跨页融资安排合计372.23 亿元人民币，较期初变动-71.40 亿元人民币；供应商已收款307.28 亿元人民币是其中一部分。</t>
   </si>
   <si>
-    <t>余额下降反驳“全部现金改善来自供应链融资新增”的解释。把全部安排一次性纳入债务的敏感性口径为1,568.24 亿元人民币；需合同条款决定信用分类。</t>
+    <t>余额是存量，不能凭其下降判断新增融资或CFO同比贡献。需按两期新增、现金结算、非现金变动及现金流分类建立桥接。全额计债仅作敏感性分析：1,568.24 亿元人民币。</t>
   </si>
   <si>
     <t>E_SUPPLY, supply_components, supply_change</t>
@@ -1385,7 +1394,7 @@
 供应商融资可替换其他资金，风险还取决于期限、集中度和终止条款。</t>
   </si>
   <si>
-    <t>取得融资机构、到期梯度及撤回条款，重算现金缺口和债务口径；不能把存量总额直接当本期CFO调整额。</t>
+    <t>核实合同分类、融资机构、到期梯度及撤回条款，重算现金缺口和债务口径；不能把存量总额直接当本期CFO调整额。</t>
   </si>
   <si>
     <t>F_LIQUIDITY</t>
@@ -1952,7 +1961,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -1967,7 +1979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1975,7 +1987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1983,7 +1995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1991,7 +2003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1999,7 +2011,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2007,7 +2019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -2015,7 +2027,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -2023,7 +2035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -2031,7 +2043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="33" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -2039,7 +2051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="18" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -2047,25 +2059,34 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" ht="18" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -2079,69 +2100,69 @@
   <sheetData>
     <row r="1" spans="1:18" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2">
         <v>423701834</v>
@@ -2154,47 +2175,47 @@
         <v>423701834000.0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2">
         <v>362012554</v>
@@ -2207,47 +2228,47 @@
         <v>362012554000.0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2">
         <v>312383297</v>
@@ -2260,47 +2281,47 @@
         <v>312383297000.0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R4" s="2"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2">
         <v>273518959</v>
@@ -2313,47 +2334,47 @@
         <v>273518959000.0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2">
         <v>76786309</v>
@@ -2366,47 +2387,47 @@
         <v>76786309000.0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D7" s="2">
         <v>54006794</v>
@@ -2419,47 +2440,47 @@
         <v>54006794000.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2">
         <v>133219982</v>
@@ -2472,47 +2493,47 @@
         <v>133219982000.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="D9" s="2">
         <v>96990345</v>
@@ -2525,47 +2546,47 @@
         <v>96990345000.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2">
         <v>299929741</v>
@@ -2578,45 +2599,45 @@
         <v>299929741000.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="D11" s="2">
         <v>270159734</v>
@@ -2629,45 +2650,45 @@
         <v>270159734000.0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" s="2">
         <v>974827544</v>
@@ -2680,45 +2701,45 @@
         <v>974827544000.0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D13" s="2">
         <v>786658123</v>
@@ -2731,45 +2752,45 @@
         <v>786658123000.0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2">
         <v>371026324</v>
@@ -2782,45 +2803,45 @@
         <v>371026324000.0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" s="2">
         <v>273456174</v>
@@ -2833,45 +2854,45 @@
         <v>273456174000.0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2">
         <v>337107747</v>
@@ -2884,45 +2905,45 @@
         <v>337107747000.0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D17" s="2">
         <v>246930033</v>
@@ -2935,45 +2956,45 @@
         <v>246930033000.0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R17" s="2"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D18" s="2">
         <v>94526239</v>
@@ -2986,45 +3007,45 @@
         <v>94526239000.0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D19" s="2">
         <v>59835533</v>
@@ -3037,45 +3058,45 @@
         <v>59835533000.0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20" s="2">
         <v>76403264</v>
@@ -3088,45 +3109,45 @@
         <v>76403264000.0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="R20" s="2"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D21" s="2">
         <v>64135510</v>
@@ -3139,45 +3160,45 @@
         <v>64135510000.0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="R21" s="2"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2">
         <v>160328962</v>
@@ -3190,45 +3211,45 @@
         <v>160328962000.0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R22" s="2"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2">
         <v>130977408</v>
@@ -3241,45 +3262,45 @@
         <v>130977408000.0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R23" s="2"/>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2">
         <v>49233377</v>
@@ -3292,45 +3313,45 @@
         <v>49233377000.0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2">
         <v>27834446</v>
@@ -3343,45 +3364,45 @@
         <v>27834446000.0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R25" s="2"/>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D26" s="2">
         <v>37222781</v>
@@ -3394,45 +3415,45 @@
         <v>37222781000.0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="R26" s="2"/>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="D27" s="2">
         <v>44362409</v>
@@ -3445,45 +3466,45 @@
         <v>44362409000.0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="R27" s="2"/>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D28" s="2">
         <v>51233080</v>
@@ -3496,45 +3517,45 @@
         <v>51233080000.0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R28" s="2"/>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="D29" s="2">
         <v>39070181</v>
@@ -3547,45 +3568,45 @@
         <v>39070181000.0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R29" s="2"/>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" s="2">
         <v>119601197</v>
@@ -3598,45 +3619,45 @@
         <v>119601197000.0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R30" s="2"/>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="D31" s="2">
         <v>136346553</v>
@@ -3649,45 +3670,45 @@
         <v>136346553000.0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R31" s="2"/>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D32" s="2">
         <v>316506369</v>
@@ -3700,47 +3721,47 @@
         <v>316506369000.0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R32" s="2"/>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="D33" s="2">
         <v>253041337</v>
@@ -3753,47 +3774,47 @@
         <v>253041337000.0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D34" s="2">
         <v>62439820</v>
@@ -3806,47 +3827,47 @@
         <v>62439820000.0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R34" s="2"/>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D35" s="2">
         <v>57290460</v>
@@ -3859,47 +3880,47 @@
         <v>57290460000.0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R35" s="2"/>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D36" s="2">
         <v>21860936</v>
@@ -3912,47 +3933,47 @@
         <v>21860936000.0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="R36" s="2"/>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D37" s="2">
         <v>28699935</v>
@@ -3965,47 +3986,47 @@
         <v>28699935000.0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="R37" s="2"/>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D38" s="2">
         <v>72201282</v>
@@ -4018,47 +4039,47 @@
         <v>72201282000.0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R38" s="2"/>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D39" s="2">
         <v>4585027</v>
@@ -4071,47 +4092,47 @@
         <v>4585027000.0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="R39" s="2"/>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D40" s="2">
         <v>-94475790</v>
@@ -4124,47 +4145,47 @@
         <v>-94475790000.0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="R40" s="2"/>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D41" s="2">
         <v>-6309543</v>
@@ -4177,47 +4198,47 @@
         <v>-6309543000.0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="R41" s="2"/>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D42" s="2">
         <v>-2664640</v>
@@ -4230,47 +4251,47 @@
         <v>-2664640000.0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="R42" s="2"/>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D43" s="2">
         <v>29770008</v>
@@ -4283,47 +4304,47 @@
         <v>29770008000.0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R43" s="2"/>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D44" s="2">
         <v>42344558</v>
@@ -4336,47 +4357,47 @@
         <v>42344558000.0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R44" s="2"/>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D45" s="2">
         <v>84006523</v>
@@ -4389,47 +4410,47 @@
         <v>84006523000.0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="R45" s="2"/>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="D46" s="2">
         <v>40416391</v>
@@ -4442,47 +4463,47 @@
         <v>40416391000.0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="R46" s="2"/>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D47" s="2">
         <v>-26842954</v>
@@ -4495,47 +4516,47 @@
         <v>-26842954000.0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R47" s="2"/>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D48" s="2">
         <v>-9811</v>
@@ -4548,47 +4569,47 @@
         <v>-9811000.0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="R48" s="2"/>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D49" s="2">
         <v>39790079</v>
@@ -4601,47 +4622,47 @@
         <v>39790079000.0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R49" s="2"/>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D50" s="2">
         <v>-54608510</v>
@@ -4654,47 +4675,47 @@
         <v>-54608510000.0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R50" s="2"/>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D51" s="2">
         <v>-1926925</v>
@@ -4707,47 +4728,47 @@
         <v>-1926925000.0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R51" s="2"/>
     </row>
     <row r="52" spans="1:18">
       <c r="A52" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D52" s="2">
         <v>2659992</v>
@@ -4760,47 +4781,47 @@
         <v>2659992000.0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="R52" s="2"/>
     </row>
     <row r="53" spans="1:18">
       <c r="A53" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="D53" s="2">
         <v>60616240</v>
@@ -4813,47 +4834,47 @@
         <v>60616240000.0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R53" s="2"/>
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D54" s="2">
         <v>603801220</v>
@@ -4866,45 +4887,45 @@
         <v>603801220000.0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="R54" s="2"/>
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D55" s="2">
         <v>333512927</v>
@@ -4917,45 +4938,45 @@
         <v>333512927000.0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="R55" s="2"/>
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D56" s="2">
         <v>33583185</v>
@@ -4968,45 +4989,45 @@
         <v>33583185000.0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P56" s="2"/>
       <c r="Q56" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="R56" s="2"/>
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D57" s="2">
         <v>18428631</v>
@@ -5019,45 +5040,45 @@
         <v>18428631000.0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R57" s="2"/>
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D58" s="2">
         <v>461587</v>
@@ -5070,45 +5091,45 @@
         <v>461587000.0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="R58" s="2"/>
     </row>
     <row r="59" spans="1:18">
       <c r="A59" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D59" s="2">
         <v>14692968</v>
@@ -5121,45 +5142,45 @@
         <v>14692968000.0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="R59" s="2"/>
     </row>
     <row r="60" spans="1:18">
       <c r="A60" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D60" s="2">
         <v>23902653</v>
@@ -5172,45 +5193,45 @@
         <v>23902653000.0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R60" s="2"/>
     </row>
     <row r="61" spans="1:18">
       <c r="A61" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D61" s="2">
         <v>13320128</v>
@@ -5223,45 +5244,45 @@
         <v>13320128000.0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="R61" s="2"/>
     </row>
     <row r="62" spans="1:18">
       <c r="A62" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D62" s="2">
         <v>30728127</v>
@@ -5274,45 +5295,45 @@
         <v>30728127000.0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="R62" s="2"/>
     </row>
     <row r="63" spans="1:18">
       <c r="A63" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D63" s="2">
         <v>2865508</v>
@@ -5325,45 +5346,45 @@
         <v>2865508000.0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="R63" s="2"/>
     </row>
     <row r="64" spans="1:18">
       <c r="A64" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D64" s="2">
         <v>205516</v>
@@ -5376,45 +5397,45 @@
         <v>205516000.0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="R64" s="2"/>
     </row>
     <row r="65" spans="1:18">
       <c r="A65" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D65" s="2">
         <v>70414214</v>
@@ -5427,47 +5448,47 @@
         <v>70414214000.0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P65" s="2"/>
       <c r="Q65" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="R65" s="2"/>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D66" s="2">
         <v>661</v>
@@ -5480,47 +5501,47 @@
         <v>661.0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:18">
       <c r="A67" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D67" s="2">
         <v>475</v>
@@ -5533,47 +5554,47 @@
         <v>475.0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D68" s="2">
         <v>8660164</v>
@@ -5586,47 +5607,47 @@
         <v>8660164000.0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="R68" s="2"/>
     </row>
     <row r="69" spans="1:18">
       <c r="A69" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D69" s="2">
         <v>418585</v>
@@ -5639,47 +5660,47 @@
         <v>418585000.0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R69" s="2"/>
     </row>
     <row r="70" spans="1:18">
       <c r="A70" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D70" s="2">
         <v>24322780</v>
@@ -5692,47 +5713,47 @@
         <v>24322780000.0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R70" s="2"/>
     </row>
     <row r="71" spans="1:18">
       <c r="A71" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D71" s="2">
         <v>337367</v>
@@ -5745,47 +5766,47 @@
         <v>337367000.0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="R71" s="2"/>
     </row>
     <row r="72" spans="1:18">
       <c r="A72" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D72" s="2">
         <v>512000</v>
@@ -5798,47 +5819,47 @@
         <v>512000000.0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="R72" s="2"/>
     </row>
     <row r="73" spans="1:18">
       <c r="A73" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D73" s="2">
         <v>1764508</v>
@@ -5851,47 +5872,47 @@
         <v>1764508000.0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R73" s="2"/>
     </row>
     <row r="74" spans="1:18">
       <c r="A74" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D74" s="2">
         <v>-174640</v>
@@ -5904,47 +5925,47 @@
         <v>-174640000.0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="R74" s="2"/>
     </row>
     <row r="75" spans="1:18">
       <c r="A75" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D75" s="2">
         <v>151291</v>
@@ -5957,47 +5978,47 @@
         <v>151291000.0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="R75" s="2"/>
     </row>
     <row r="76" spans="1:18">
       <c r="A76" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D76" s="2">
         <v>-974079</v>
@@ -6010,47 +6031,47 @@
         <v>-974079000.0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="R76" s="2"/>
     </row>
     <row r="77" spans="1:18">
       <c r="A77" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D77" s="2">
         <v>2470751</v>
@@ -6063,47 +6084,47 @@
         <v>2470751000.0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="R77" s="2"/>
     </row>
     <row r="78" spans="1:18">
       <c r="A78" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D78" s="2">
         <v>-8429599</v>
@@ -6116,47 +6137,47 @@
         <v>-8429599000.0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P78" s="2"/>
       <c r="Q78" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="R78" s="2"/>
     </row>
     <row r="79" spans="1:18">
       <c r="A79" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D79" s="2">
         <v>-7660090</v>
@@ -6169,47 +6190,47 @@
         <v>-7660090000.0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P79" s="2"/>
       <c r="Q79" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R79" s="2"/>
     </row>
     <row r="80" spans="1:18">
       <c r="A80" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D80" s="2">
         <v>1900952</v>
@@ -6222,47 +6243,47 @@
         <v>1900952000.0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R80" s="2"/>
     </row>
     <row r="81" spans="1:18">
       <c r="A81" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D81" s="2">
         <v>-39837988</v>
@@ -6275,47 +6296,47 @@
         <v>-39837988000.0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="R81" s="2"/>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D82" s="2">
         <v>-16911542</v>
@@ -6328,47 +6349,47 @@
         <v>-16911542000.0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R82" s="2"/>
     </row>
     <row r="83" spans="1:18">
       <c r="A83" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D83" s="2">
         <v>89965735</v>
@@ -6381,47 +6402,47 @@
         <v>89965735000.0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="R83" s="2"/>
     </row>
     <row r="84" spans="1:18">
       <c r="A84" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D84" s="2">
         <v>-82524</v>
@@ -6434,35 +6455,35 @@
         <v>-82524000.0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P84" s="2"/>
       <c r="Q84" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="R84" s="2"/>
     </row>
@@ -6474,68 +6495,83 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="15" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" customWidth="1"/>
+    <col min="4" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="15" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D2" s="3">
         <f>(('Facts'!F2-'Facts'!F4))*1</f>
@@ -6554,46 +6590,46 @@
         <v/>
       </c>
       <c r="H2" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K2" s="2">
         <v>1000</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D3" s="3">
         <f>IF('Facts'!F2&lt;=0,NA(),(('Calculations'!D2/'Facts'!F2))*1)</f>
         <v>0.26272847570445024</v>
       </c>
       <c r="E3" s="4">
-        <f>D3/K3</f>
+        <f>D3</f>
         <v>0.26272847570445024</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -6605,46 +6641,46 @@
         <v/>
       </c>
       <c r="H3" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D4" s="3">
         <f>IF(OR('Facts'!F3&lt;=0,'Facts'!F2&lt;0),NA(),((('Facts'!F2-'Facts'!F3)/'Facts'!F3))*1)</f>
         <v>0.1704064660696822</v>
       </c>
       <c r="E4" s="4">
-        <f>D4/K4</f>
+        <f>D4</f>
         <v>0.1704064660696822</v>
       </c>
       <c r="F4" s="2" t="str">
@@ -6656,46 +6692,46 @@
         <v/>
       </c>
       <c r="H4" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D5" s="3">
         <f>IF(OR('Facts'!F7&lt;=0,'Facts'!F6&lt;0),NA(),((('Facts'!F6-'Facts'!F7)/'Facts'!F7))*1)</f>
         <v>0.42178980296441965</v>
       </c>
       <c r="E5" s="4">
-        <f>D5/K5</f>
+        <f>D5</f>
         <v>0.42178980296441965</v>
       </c>
       <c r="F5" s="2" t="str">
@@ -6707,46 +6743,46 @@
         <v/>
       </c>
       <c r="H5" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D6" s="3">
         <f>IF(OR('Facts'!F9&lt;=0,'Facts'!F8&lt;0),NA(),((('Facts'!F8-'Facts'!F9)/'Facts'!F9))*1)</f>
         <v>0.3735385929393281</v>
       </c>
       <c r="E6" s="4">
-        <f>D6/K6</f>
+        <f>D6</f>
         <v>0.3735385929393281</v>
       </c>
       <c r="F6" s="2" t="str">
@@ -6758,46 +6794,46 @@
         <v/>
       </c>
       <c r="H6" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D7" s="3">
         <f>IF(OR('Facts'!F33&lt;=0,'Facts'!F32&lt;0),NA(),((('Facts'!F32-'Facts'!F33)/'Facts'!F33))*1)</f>
         <v>0.2508089498436376</v>
       </c>
       <c r="E7" s="4">
-        <f>D7/K7</f>
+        <f>D7</f>
         <v>0.2508089498436376</v>
       </c>
       <c r="F7" s="2" t="str">
@@ -6809,46 +6845,46 @@
         <v/>
       </c>
       <c r="H7" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D8" s="3">
         <f>IF(OR('Facts'!F35&lt;=0,'Facts'!F34&lt;0),NA(),((('Facts'!F34-'Facts'!F35)/'Facts'!F35))*1)</f>
         <v>0.0898816312523935</v>
       </c>
       <c r="E8" s="4">
-        <f>D8/K8</f>
+        <f>D8</f>
         <v>0.0898816312523935</v>
       </c>
       <c r="F8" s="2" t="str">
@@ -6860,46 +6896,46 @@
         <v/>
       </c>
       <c r="H8" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D9" s="3">
         <f>IF(OR('Facts'!F37&lt;=0,'Facts'!F36&lt;0),NA(),((('Facts'!F36-'Facts'!F37)/'Facts'!F37))*1)</f>
         <v>-0.23829318777202804</v>
       </c>
       <c r="E9" s="4">
-        <f>D9/K9</f>
+        <f>D9</f>
         <v>-0.23829318777202804</v>
       </c>
       <c r="F9" s="2" t="str">
@@ -6911,46 +6947,46 @@
         <v/>
       </c>
       <c r="H9" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D10" s="3">
         <f>IF(OR('Facts'!F67&lt;=0,'Facts'!F66&lt;0),NA(),((('Facts'!F66-'Facts'!F67)/'Facts'!F67))*1)</f>
         <v>0.391578947368421</v>
       </c>
       <c r="E10" s="4">
-        <f>D10/K10</f>
+        <f>D10</f>
         <v>0.391578947368421</v>
       </c>
       <c r="F10" s="2" t="str">
@@ -6962,46 +6998,46 @@
         <v/>
       </c>
       <c r="H10" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D11" s="3">
         <f>IF('Facts'!F6&lt;=0,NA(),(('Facts'!F8/'Facts'!F6))*1)</f>
         <v>1.7349444677696384</v>
       </c>
       <c r="E11" s="4">
-        <f>D11/K11</f>
+        <f>D11</f>
         <v>1.7349444677696384</v>
       </c>
       <c r="F11" s="2" t="str">
@@ -7013,39 +7049,39 @@
         <v/>
       </c>
       <c r="H11" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D12" s="3">
         <f>(('Facts'!F6*1)+('Facts'!F68*1)+('Facts'!F69*1)+('Facts'!F70*1)+('Facts'!F71*1)+('Facts'!F72*1)+('Facts'!F73*1)+('Facts'!F74*1)+('Facts'!F75*1)+('Facts'!F76*1)+('Facts'!F77*1)+('Facts'!F78*1)+('Facts'!F79*1)+('Facts'!F80*1)+('Facts'!F81*1)+('Facts'!F82*1)+('Facts'!F83*1)+('Facts'!F84*1))*1</f>
@@ -7064,39 +7100,39 @@
         <v/>
       </c>
       <c r="H12" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K12" s="2">
         <v>1000</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D13" s="3">
         <f>(('Facts'!F81*1)+('Facts'!F82*1)+('Facts'!F83*1))*1</f>
@@ -7115,39 +7151,39 @@
         <v/>
       </c>
       <c r="H13" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K13" s="2">
         <v>1000</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D14" s="3">
         <f>(('Facts'!F8-'Facts'!F44))*1</f>
@@ -7166,39 +7202,39 @@
         <v/>
       </c>
       <c r="H14" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K14" s="2">
         <v>1000</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D15" s="3">
         <f>(('Facts'!F8*1)+('Facts'!F40*1)+('Facts'!F41*1)+('Facts'!F42*1))*1</f>
@@ -7217,39 +7253,39 @@
         <v/>
       </c>
       <c r="H15" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K15" s="2">
         <v>1000</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D16" s="3">
         <f>(('Facts'!F11*1)+('Facts'!F8*1)+('Facts'!F40*1)+('Facts'!F41*1)+('Facts'!F42*1))*1</f>
@@ -7268,39 +7304,39 @@
         <v/>
       </c>
       <c r="H16" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K16" s="2">
         <v>1000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D17" s="3">
         <f>(('Facts'!F54*1)+('Facts'!F14*1))*1</f>
@@ -7319,37 +7355,37 @@
         <v/>
       </c>
       <c r="H17" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K17" s="2">
         <v>1000</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D18" s="3">
         <f>(('Facts'!F38*1)+('Facts'!F39*1))*1</f>
@@ -7368,39 +7404,39 @@
         <v/>
       </c>
       <c r="H18" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K18" s="2">
         <v>1000</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D19" s="3">
         <f>(('Facts'!F15*1)+('Facts'!F45*1)+('Facts'!F46*1)+('Facts'!F47*1)+('Facts'!F48*1))*1</f>
@@ -7419,39 +7455,39 @@
         <v/>
       </c>
       <c r="H19" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K19" s="2">
         <v>1000</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D20" s="3">
         <f>(('Facts'!F31*1)+('Facts'!F49*1)+('Facts'!F50*1)+('Facts'!F51*1))*1</f>
@@ -7470,39 +7506,39 @@
         <v/>
       </c>
       <c r="H20" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K20" s="2">
         <v>1000</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D21" s="3">
         <f>(('Facts'!F60*1)+('Facts'!F61*1))*1</f>
@@ -7521,37 +7557,37 @@
         <v/>
       </c>
       <c r="H21" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K21" s="2">
         <v>1000</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D22" s="3">
         <f>(('Facts'!F26-'Facts'!F27))*1</f>
@@ -7570,37 +7606,37 @@
         <v/>
       </c>
       <c r="H22" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K22" s="2">
         <v>1000</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D23" s="3">
         <f>(('Facts'!F10*1)+('Facts'!F56*1))*1</f>
@@ -7619,37 +7655,37 @@
         <v/>
       </c>
       <c r="H23" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K23" s="2">
         <v>1000</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D24" s="3">
         <f>(('Facts'!F57*1)+('Facts'!F58*1)+('Facts'!F59*1))*1</f>
@@ -7668,37 +7704,37 @@
         <v/>
       </c>
       <c r="H24" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K24" s="2">
         <v>1000</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D25" s="3">
         <f>(('Facts'!F30*1)+('Facts'!F26*1))*1</f>
@@ -7717,37 +7753,37 @@
         <v/>
       </c>
       <c r="H25" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K25" s="2">
         <v>1000</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D26" s="3">
         <f>(AVERAGE('Facts'!F17,'Facts'!F16))*1</f>
@@ -7766,46 +7802,46 @@
         <v/>
       </c>
       <c r="H26" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K26" s="2">
         <v>1000</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D27" s="3">
         <f>IF('Calculations'!D26&lt;=0,NA(),(('Facts'!F38/'Calculations'!D26))*1)</f>
         <v>0.24724866942683058</v>
       </c>
       <c r="E27" s="4">
-        <f>D27/K27</f>
+        <f>D27</f>
         <v>0.24724866942683058</v>
       </c>
       <c r="F27" s="2" t="str">
@@ -7817,39 +7853,39 @@
         <v/>
       </c>
       <c r="H27" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D28" s="3">
         <f>(('Facts'!F63-'Facts'!F64))*1</f>
@@ -7868,88 +7904,99 @@
         <v/>
       </c>
       <c r="H28" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K28" s="2">
         <v>1000</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O28"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="38.7109375" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="48" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" s="3">
+        <v>76</v>
+      </c>
+      <c r="E2" s="2">
         <f>ROUND('Calculations'!D17-'Facts'!F12,J2)</f>
         <v>0.0</v>
       </c>
@@ -7961,7 +8008,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I2" s="2">
         <f>IF(ISNUMBER(E2),"","missing or unavailable input")</f>
@@ -7971,20 +8018,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="48" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="3">
+        <v>60</v>
+      </c>
+      <c r="E3" s="2">
         <f>ROUND('Calculations'!D18-'Facts'!F6,J3)</f>
         <v>0.0</v>
       </c>
@@ -7996,7 +8043,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I3" s="2">
         <f>IF(ISNUMBER(E3),"","missing or unavailable input")</f>
@@ -8006,20 +8053,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" ht="48" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="3">
+        <v>65</v>
+      </c>
+      <c r="E4" s="2">
         <f>ROUND('Calculations'!D12-'Facts'!F8,J4)</f>
         <v>-2000.0</v>
       </c>
@@ -8031,7 +8078,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I4" s="2">
         <f>IF(ISNUMBER(E4),"","missing or unavailable input")</f>
@@ -8041,20 +8088,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="48" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E5" s="3">
+        <v>143</v>
+      </c>
+      <c r="E5" s="2">
         <f>ROUND('Calculations'!D15-'Facts'!F43,J5)</f>
         <v>1000.0</v>
       </c>
@@ -8066,7 +8113,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I5" s="2">
         <f>IF(ISNUMBER(E5),"","missing or unavailable input")</f>
@@ -8076,20 +8123,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="48" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="3">
+        <v>70</v>
+      </c>
+      <c r="E6" s="2">
         <f>ROUND('Calculations'!D16-'Facts'!F10,J6)</f>
         <v>2000.0</v>
       </c>
@@ -8101,7 +8148,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I6" s="2">
         <f>IF(ISNUMBER(E6),"","missing or unavailable input")</f>
@@ -8111,20 +8158,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" ht="48" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="3">
+        <v>81</v>
+      </c>
+      <c r="E7" s="2">
         <f>ROUND('Calculations'!D19-'Facts'!F14,J7)</f>
         <v>-1000.0</v>
       </c>
@@ -8136,7 +8183,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I7" s="2">
         <f>IF(ISNUMBER(E7),"","missing or unavailable input")</f>
@@ -8146,20 +8193,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" ht="48" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="3">
+        <v>115</v>
+      </c>
+      <c r="E8" s="2">
         <f>ROUND('Calculations'!D20-'Facts'!F30,J8)</f>
         <v>0.0</v>
       </c>
@@ -8171,7 +8218,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I8" s="2">
         <f>IF(ISNUMBER(E8),"","missing or unavailable input")</f>
@@ -8181,20 +8228,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="48" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="3">
+        <v>105</v>
+      </c>
+      <c r="E9" s="2">
         <f>ROUND('Calculations'!D21-'Facts'!F26,J9)</f>
         <v>0.0</v>
       </c>
@@ -8206,7 +8253,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I9" s="2">
         <f>IF(ISNUMBER(E9),"","missing or unavailable input")</f>
@@ -8216,20 +8263,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="48" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="3">
+        <v>169</v>
+      </c>
+      <c r="E10" s="2">
         <f>ROUND('Calculations'!D23-'Facts'!F55,J10)</f>
         <v>-1000.0</v>
       </c>
@@ -8241,7 +8288,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I10" s="2">
         <f>IF(ISNUMBER(E10),"","missing or unavailable input")</f>
@@ -8251,20 +8298,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="48" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" s="3">
+        <v>171</v>
+      </c>
+      <c r="E11" s="2">
         <f>ROUND('Calculations'!D24-'Facts'!F56,J11)</f>
         <v>1000.0</v>
       </c>
@@ -8276,7 +8323,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I11" s="2">
         <f>IF(ISNUMBER(E11),"","missing or unavailable input")</f>
@@ -8288,7 +8335,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J11"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -8306,39 +8354,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -8361,240 +8409,240 @@
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -8619,226 +8667,226 @@
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -8857,96 +8905,96 @@
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -8969,62 +9017,62 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
